--- a/performance.xlsx
+++ b/performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuchangi/Documents/AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C1EB4D-1254-EE43-852E-47A5E6CAA76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56540B0A-5B3C-9940-8203-02BF948EA78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19820" xr2:uid="{5DD09CA2-2D04-AF4E-961C-068B7AAA015E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>zhiyi</t>
   </si>
@@ -59,9 +59,6 @@
     <t>学习</t>
   </si>
   <si>
-    <t>饮食健康</t>
-  </si>
-  <si>
     <t>你这再样，我就XXX</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
     <t>不抱怨</t>
   </si>
   <si>
-    <t>欣赏别人</t>
-  </si>
-  <si>
     <t>帮助别人</t>
   </si>
   <si>
@@ -162,6 +156,18 @@
   </si>
   <si>
     <t>其他突破 值得表扬的地方</t>
+  </si>
+  <si>
+    <t>滚</t>
+  </si>
+  <si>
+    <t>饮食健康 吃得快 不挑食</t>
+  </si>
+  <si>
+    <t>欣赏别人 看别人的长处</t>
+  </si>
+  <si>
+    <t>不双标 宽容别人</t>
   </si>
 </sst>
 </file>
@@ -541,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C342EE7-B48F-4549-9A88-4D7716B21101}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="27" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.1640625" style="1" customWidth="1"/>
@@ -571,13 +577,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -585,109 +591,112 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>5</v>
@@ -695,52 +704,60 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuchangi/Documents/AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56540B0A-5B3C-9940-8203-02BF948EA78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAFE084-D159-AC4D-B448-C73D8E2B2133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19820" xr2:uid="{5DD09CA2-2D04-AF4E-961C-068B7AAA015E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>zhiyi</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>不双标 宽容别人</t>
+  </si>
+  <si>
+    <t>其他脏话</t>
   </si>
 </sst>
 </file>
@@ -637,6 +640,9 @@
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuchangi/Documents/AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAFE084-D159-AC4D-B448-C73D8E2B2133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB3BD40-699C-D648-9EF2-DAA00D50CD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19820" xr2:uid="{5DD09CA2-2D04-AF4E-961C-068B7AAA015E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>zhiyi</t>
   </si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>不双标 宽容别人</t>
-  </si>
-  <si>
-    <t>其他脏话</t>
   </si>
 </sst>
 </file>
@@ -640,9 +637,6 @@
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>43</v>
-      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuchangi/Documents/AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB3BD40-699C-D648-9EF2-DAA00D50CD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0638411A-33E9-5E4A-9854-A2769E5EDFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19820" xr2:uid="{5DD09CA2-2D04-AF4E-961C-068B7AAA015E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>zhiyi</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>不双标 宽容别人</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -547,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C342EE7-B48F-4549-9A88-4D7716B21101}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="27" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.1640625" style="1" customWidth="1"/>
@@ -751,6 +754,9 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
@@ -758,6 +764,11 @@
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuchangi/Documents/AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0638411A-33E9-5E4A-9854-A2769E5EDFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C856646F-C12A-9B4A-910C-7B0F7740637A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19820" xr2:uid="{5DD09CA2-2D04-AF4E-961C-068B7AAA015E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
   <si>
     <t>zhiyi</t>
   </si>
@@ -550,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C342EE7-B48F-4549-9A88-4D7716B21101}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="27" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.1640625" style="1" customWidth="1"/>
@@ -640,6 +640,9 @@
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
@@ -754,9 +757,6 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
@@ -764,11 +764,6 @@
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuchangi/Documents/AI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C856646F-C12A-9B4A-910C-7B0F7740637A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1916AB7B-0D3C-FF4C-8FA7-893881B7A619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19820" xr2:uid="{5DD09CA2-2D04-AF4E-961C-068B7AAA015E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>zhiyi</t>
   </si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>不双标 宽容别人</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
 </sst>
 </file>
@@ -640,9 +637,6 @@
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>43</v>
-      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>zhiyi</t>
   </si>
@@ -81,13 +81,10 @@
     <t xml:space="preserve">学会move on</t>
   </si>
   <si>
-    <t>老哥很蠢</t>
+    <t xml:space="preserve">老哥很蠢 / 你很蠢</t>
   </si>
   <si>
     <t>把人往好处想</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>不打人</t>
@@ -164,7 +161,6 @@
     </font>
     <font>
       <sz val="20.000000"/>
-      <color indexed="64"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
@@ -789,24 +785,22 @@
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" ht="24">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="24">
       <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" ht="24">
@@ -814,36 +808,36 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" ht="24">
       <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="13" ht="24">
       <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="14" ht="24">
       <c r="A14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15" ht="24">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -851,60 +845,60 @@
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="24">
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" ht="24">
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">学会move on</t>
   </si>
   <si>
-    <t xml:space="preserve">老哥很蠢 / 你很蠢</t>
+    <t xml:space="preserve">老哥很蠢 / 老弟很蠢 / 你很蠢</t>
   </si>
   <si>
     <t>把人往好处想</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">写字姿势对 保护眼睛</t>
   </si>
   <si>
-    <t xml:space="preserve">不强嘴 白眼 跺脚 斗鸡</t>
+    <t xml:space="preserve">不犟嘴 白眼 跺脚 斗鸡</t>
   </si>
   <si>
     <t xml:space="preserve">不大叫 不拍桌子 </t>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>zhiyi</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>把人往好处想</t>
+  </si>
+  <si>
+    <t xml:space="preserve">佩奇很坏 / X很坏</t>
   </si>
   <si>
     <t>不打人</t>
@@ -785,22 +788,24 @@
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="9" ht="24">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="24">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" ht="24">
@@ -808,36 +813,36 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" ht="24">
       <c r="A12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="24">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" ht="24">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="24">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -845,60 +850,60 @@
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" ht="24">
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" ht="24">
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>zhiyi</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>不打人</t>
+  </si>
+  <si>
+    <t>什么XXX</t>
   </si>
   <si>
     <t>多说好的呀</t>
@@ -799,13 +802,16 @@
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" ht="24">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="24">
@@ -813,36 +819,36 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" ht="24">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="24">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" ht="24">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="24">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -850,60 +856,60 @@
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" ht="24">
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" ht="24">
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>zhiyi</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t xml:space="preserve">更自信 更勇敢 更礼貌</t>
+  </si>
+  <si>
+    <t>啊啊啊啊啊</t>
   </si>
   <si>
     <t>更坚强</t>
@@ -813,42 +816,45 @@
       <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="11" ht="24">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="24">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" ht="24">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="24">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" ht="24">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
@@ -856,7 +862,7 @@
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>26</v>
@@ -864,52 +870,52 @@
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" ht="24">
       <c r="B22" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" ht="24">
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>zhiyi</t>
   </si>
@@ -39,6 +39,12 @@
     <t>XXX，吧吧怪</t>
   </si>
   <si>
+    <t xml:space="preserve">饮食健康 吃得快 不挑食</t>
+  </si>
+  <si>
+    <t xml:space="preserve">起床主动迅速 自己穿衣</t>
+  </si>
+  <si>
     <t>学习</t>
   </si>
   <si>
@@ -48,7 +54,7 @@
     <t>你这再样，我就XXX</t>
   </si>
   <si>
-    <t xml:space="preserve">饮食健康 吃得快 不挑食</t>
+    <t>考虑问题全面</t>
   </si>
   <si>
     <t>说话解决问题</t>
@@ -115,9 +121,6 @@
   </si>
   <si>
     <t xml:space="preserve">拒绝诱惑 零食有节制 少吃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">起床主动迅速 自己穿衣</t>
   </si>
   <si>
     <t xml:space="preserve">欣赏别人 看别人的长处</t>
@@ -731,191 +734,197 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" ht="24">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="24">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="24">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="24">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="24">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="24">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="24">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" ht="24">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="24">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" ht="24">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="24">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" ht="24">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" ht="24">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" ht="24">
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" ht="24">
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>zhiyi</t>
   </si>
@@ -114,6 +114,9 @@
     <t>更坚强</t>
   </si>
   <si>
+    <t>老爸最不知道</t>
+  </si>
+  <si>
     <t>不抱怨</t>
   </si>
   <si>
@@ -144,7 +147,7 @@
     <t xml:space="preserve">不犟嘴 白眼 跺脚 斗鸡</t>
   </si>
   <si>
-    <t xml:space="preserve">不大叫 不拍桌子 </t>
+    <t xml:space="preserve">不大叫 不跺脚 不拍桌子 </t>
   </si>
   <si>
     <t xml:space="preserve">稳重 不追逐打闹 不重复别人的话</t>
@@ -836,18 +839,21 @@
       <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="12" ht="24">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="24">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -855,15 +861,15 @@
     </row>
     <row r="14" ht="24">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" ht="24">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
@@ -871,7 +877,7 @@
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -879,52 +885,52 @@
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" ht="24">
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" ht="24">
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -147,7 +147,7 @@
     <t xml:space="preserve">不犟嘴 白眼 跺脚 斗鸡</t>
   </si>
   <si>
-    <t xml:space="preserve">不大叫 不跺脚 不拍桌子 </t>
+    <t xml:space="preserve">不大叫 不指人 不跺脚 不拍桌子 </t>
   </si>
   <si>
     <t xml:space="preserve">稳重 不追逐打闹 不重复别人的话</t>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -147,7 +147,7 @@
     <t xml:space="preserve">不犟嘴 白眼 跺脚 斗鸡</t>
   </si>
   <si>
-    <t xml:space="preserve">不大叫 不指人 不跺脚 不拍桌子 </t>
+    <t xml:space="preserve">不大叫 不指人 不吐舌头 不跺脚 不拍桌子 </t>
   </si>
   <si>
     <t xml:space="preserve">稳重 不追逐打闹 不重复别人的话</t>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>zhiyi</t>
   </si>
@@ -114,13 +114,16 @@
     <t>更坚强</t>
   </si>
   <si>
-    <t>老爸最不知道</t>
+    <t>XX最不知道</t>
   </si>
   <si>
     <t>不抱怨</t>
   </si>
   <si>
     <t xml:space="preserve">不说反话 不说气话</t>
+  </si>
+  <si>
+    <t>XX我最不喜欢你</t>
   </si>
   <si>
     <t xml:space="preserve">拒绝诱惑 零食有节制 少吃</t>
@@ -850,10 +853,13 @@
       <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="C12" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" ht="24">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -861,15 +867,15 @@
     </row>
     <row r="14" ht="24">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="24">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
@@ -877,7 +883,7 @@
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -885,52 +891,52 @@
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="24">
       <c r="B22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" ht="24">
       <c r="B23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -126,7 +126,7 @@
     <t>XX我最不喜欢你</t>
   </si>
   <si>
-    <t xml:space="preserve">拒绝诱惑 零食有节制 少吃</t>
+    <t xml:space="preserve">拒绝诱惑 不吃零食</t>
   </si>
   <si>
     <t xml:space="preserve">欣赏别人 看别人的长处</t>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>zhiyi</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t xml:space="preserve">稳重 不追逐打闹 不变声说话</t>
+  </si>
+  <si>
+    <t xml:space="preserve">管好我自己 不要管别人</t>
   </si>
   <si>
     <t xml:space="preserve">其他突破 值得表扬的地方</t>
@@ -930,6 +933,9 @@
       </c>
     </row>
     <row r="22" ht="24">
+      <c r="A22" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="B22" s="1" t="s">
         <v>47</v>
       </c>
@@ -937,6 +943,11 @@
     <row r="23" ht="24">
       <c r="B23" s="1" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="24" ht="24">
+      <c r="B24" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>zhiyi</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t xml:space="preserve">其他突破 值得表扬的地方</t>
+  </si>
+  <si>
+    <t>不扣杀球</t>
   </si>
 </sst>
 </file>
@@ -207,10 +210,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -941,12 +945,18 @@
       </c>
     </row>
     <row r="23" ht="24">
+      <c r="A23" s="2"/>
       <c r="B23" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" ht="32.25" customHeight="1">
+      <c r="B24" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" ht="24">
-      <c r="B24" s="1" t="s">
+    <row r="25" ht="24">
+      <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
     </row>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>zhiyi</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t xml:space="preserve">拒绝诱惑 不吃零食</t>
+  </si>
+  <si>
+    <t>其他没意义的话</t>
   </si>
   <si>
     <t xml:space="preserve">欣赏别人 看别人的长处</t>
@@ -210,11 +213,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -871,18 +873,21 @@
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" ht="24">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="24">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
@@ -890,7 +895,7 @@
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -898,39 +903,39 @@
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>36</v>
@@ -938,26 +943,26 @@
     </row>
     <row r="22" ht="24">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" ht="24">
-      <c r="A23" s="2"/>
+      <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" ht="32.25" customHeight="1">
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" ht="24">
       <c r="B25" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>zhiyi</t>
   </si>
@@ -132,7 +132,7 @@
     <t>其他没意义的话</t>
   </si>
   <si>
-    <t xml:space="preserve">欣赏别人 看别人的长处</t>
+    <t xml:space="preserve">欣赏弟弟 看弟弟的长处</t>
   </si>
   <si>
     <t>不学所有人错的</t>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>不扣杀球</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欣赏哥哥 看哥哥的长处</t>
   </si>
 </sst>
 </file>
@@ -960,8 +963,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" ht="24">
+    <row r="25" ht="32.25" customHeight="1">
       <c r="B25" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" ht="24">
+      <c r="B26" s="1" t="s">
         <v>51</v>
       </c>
     </row>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>zhiyi</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t xml:space="preserve">管好我自己 不要管别人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">说错了 就用正确的方式再说一遍</t>
   </si>
   <si>
     <t xml:space="preserve">其他突破 值得表扬的地方</t>
@@ -949,28 +952,36 @@
         <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" ht="24">
+      <c r="A23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" ht="24">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" ht="32.25" customHeight="1">
+    <row r="24" ht="24">
+      <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" ht="32.25" customHeight="1">
       <c r="B25" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" ht="24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" ht="32.25" customHeight="1">
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" ht="24">
+      <c r="B27" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -141,7 +141,7 @@
     <t>帮助别人</t>
   </si>
   <si>
-    <t>不强迫症</t>
+    <t xml:space="preserve">不强迫症 不感官过载</t>
   </si>
   <si>
     <t>做弟弟好榜样</t>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>zhiyi</t>
   </si>
@@ -129,13 +129,16 @@
     <t xml:space="preserve">拒绝诱惑 不吃零食</t>
   </si>
   <si>
+    <t>XX你太坏了</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欣赏弟弟 看弟弟的长处</t>
+  </si>
+  <si>
+    <t>不学所有人错的</t>
+  </si>
+  <si>
     <t>其他没意义的话</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欣赏弟弟 看弟弟的长处</t>
-  </si>
-  <si>
-    <t>不学所有人错的</t>
   </si>
   <si>
     <t>帮助别人</t>
@@ -890,10 +893,13 @@
       <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" ht="24">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
@@ -901,7 +907,7 @@
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -909,39 +915,39 @@
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>36</v>
@@ -949,39 +955,39 @@
     </row>
     <row r="22" ht="24">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" ht="24">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" ht="24">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" ht="32.25" customHeight="1">
       <c r="B25" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" ht="32.25" customHeight="1">
       <c r="B26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" ht="24">
       <c r="B27" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/performance.xlsx
+++ b/performance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>zhiyi</t>
   </si>
@@ -138,10 +138,13 @@
     <t>不学所有人错的</t>
   </si>
   <si>
+    <t>不听劝地说老爸老妈老哥老弟</t>
+  </si>
+  <si>
+    <t>帮助别人</t>
+  </si>
+  <si>
     <t>其他没意义的话</t>
-  </si>
-  <si>
-    <t>帮助别人</t>
   </si>
   <si>
     <t xml:space="preserve">不强迫症 不感官过载</t>
@@ -904,10 +907,13 @@
       <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="16" ht="24">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>28</v>
@@ -915,39 +921,39 @@
     </row>
     <row r="17" ht="24">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" ht="24">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" ht="24">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" ht="24">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" ht="24">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>36</v>
@@ -955,39 +961,39 @@
     </row>
     <row r="22" ht="24">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" ht="24">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" ht="24">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" ht="32.25" customHeight="1">
       <c r="B25" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" ht="32.25" customHeight="1">
       <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" ht="24">
       <c r="B27" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
